--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>6.589369058609009</v>
+        <v>6.7656378746032715</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>6.7656378746032715</v>
+        <v>5.6402318477630615</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.6402318477630615</v>
+        <v>5.40358304977417</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.40358304977417</v>
+        <v>5.311929941177368</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.311929941177368</v>
+        <v>5.772078990936279</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.772078990936279</v>
+        <v>5.625236988067627</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.625236988067627</v>
+        <v>5.684807062149048</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -531,25 +531,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.703763714412599</v>
+        <v>-0.7037637142061097</v>
       </c>
       <c r="C2">
-        <v>0.30119918524606115</v>
+        <v>0.3011991852586056</v>
       </c>
       <c r="D2">
-        <v>-2.3365392367767113</v>
+        <v>-2.336539235993841</v>
       </c>
       <c r="E2">
-        <v>0.01946315513166863</v>
+        <v>0.019463155172418922</v>
       </c>
       <c r="F2">
-        <v>0.3055125217238755</v>
+        <v>0.30551252174175614</v>
       </c>
       <c r="G2">
-        <v>-2.303551129235436</v>
+        <v>-2.303551128424738</v>
       </c>
       <c r="H2">
-        <v>0.02124785389045636</v>
+        <v>0.021247853936011696</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -557,25 +557,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.2382051956548254</v>
+        <v>0.23820519568154344</v>
       </c>
       <c r="C3">
-        <v>0.07760607900215175</v>
+        <v>0.07760607900483765</v>
       </c>
       <c r="D3">
-        <v>3.0694141324704836</v>
+        <v>3.06941413270853</v>
       </c>
       <c r="E3">
-        <v>0.002144790512581096</v>
+        <v>0.002144790510871797</v>
       </c>
       <c r="F3">
-        <v>0.07824848493912467</v>
+        <v>0.07824848494366893</v>
       </c>
       <c r="G3">
-        <v>3.044214796492775</v>
+        <v>3.0442147966574344</v>
       </c>
       <c r="H3">
-        <v>0.002332885105807092</v>
+        <v>0.0023328851045301136</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -583,25 +583,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0.3903224838773774</v>
+        <v>0.3903224840538546</v>
       </c>
       <c r="C4">
-        <v>0.43666600746882295</v>
+        <v>0.4366660074934905</v>
       </c>
       <c r="D4">
-        <v>0.8938696330862109</v>
+        <v>0.8938696334398625</v>
       </c>
       <c r="E4">
-        <v>0.3713916470439198</v>
+        <v>0.3713916468546792</v>
       </c>
       <c r="F4">
-        <v>0.43422802935195615</v>
+        <v>0.43422802938429883</v>
       </c>
       <c r="G4">
-        <v>0.8988882741169344</v>
+        <v>0.8988882744563983</v>
       </c>
       <c r="H4">
-        <v>0.3687121743666575</v>
+        <v>0.36871217418582414</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -609,25 +609,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.26968892553493873</v>
+        <v>0.26968892564207503</v>
       </c>
       <c r="C5">
-        <v>0.10371022776334678</v>
+        <v>0.10371022776898316</v>
       </c>
       <c r="D5">
-        <v>2.600408188769325</v>
+        <v>2.6004081896610343</v>
       </c>
       <c r="E5">
-        <v>0.009311293098910767</v>
+        <v>0.009311293074712346</v>
       </c>
       <c r="F5">
-        <v>0.1051152500368105</v>
+        <v>0.10511525004532384</v>
       </c>
       <c r="G5">
-        <v>2.5656498504307974</v>
+        <v>2.565649851242231</v>
       </c>
       <c r="H5">
-        <v>0.010298272782127471</v>
+        <v>0.010298272758038962</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -661,25 +661,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>-1.6663402005328123</v>
+        <v>-1.6663402004702617</v>
       </c>
       <c r="C7">
-        <v>0.29991493864047275</v>
+        <v>0.2999149386510303</v>
       </c>
       <c r="D7">
-        <v>-5.556042683590233</v>
+        <v>-5.556042683186089</v>
       </c>
       <c r="E7">
         <v>2.7595941753943976e-8</v>
       </c>
       <c r="F7">
-        <v>0.3006612280071006</v>
+        <v>0.3006612280226732</v>
       </c>
       <c r="G7">
-        <v>-5.5422516949656675</v>
+        <v>-5.542251694470566</v>
       </c>
       <c r="H7">
-        <v>2.9860666828085414e-8</v>
+        <v>2.986066705013002e-8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -687,25 +687,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.1798076028828576</v>
+        <v>0.17980760302441526</v>
       </c>
       <c r="C8">
-        <v>0.06778456517149449</v>
+        <v>0.06778456517329749</v>
       </c>
       <c r="D8">
-        <v>2.6526334192444194</v>
+        <v>2.6526334212622085</v>
       </c>
       <c r="E8">
-        <v>0.007986655703159151</v>
+        <v>0.007986655655420893</v>
       </c>
       <c r="F8">
-        <v>0.0675955335133092</v>
+        <v>0.0675955335164646</v>
       </c>
       <c r="G8">
-        <v>2.6600515379829712</v>
+        <v>2.6600515399529847</v>
       </c>
       <c r="H8">
-        <v>0.007812869536530043</v>
+        <v>0.007812869490831487</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -713,22 +713,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-0.6030142469453168</v>
+        <v>-0.6030142469669489</v>
       </c>
       <c r="C9">
-        <v>0.02892952730149283</v>
+        <v>0.028929527299784954</v>
       </c>
       <c r="D9">
-        <v>-20.844248184940092</v>
+        <v>-20.844248186918403</v>
       </c>
       <c r="E9">
         <v>0.0</v>
       </c>
       <c r="F9">
-        <v>0.030175273263131155</v>
+        <v>0.030175273262587524</v>
       </c>
       <c r="G9">
-        <v>-19.983721164245214</v>
+        <v>-19.98372116532212</v>
       </c>
       <c r="H9">
         <v>0.0</v>
@@ -739,22 +739,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>-0.016973230503702155</v>
+        <v>-0.016973230506720775</v>
       </c>
       <c r="C10">
-        <v>0.002082061388365985</v>
+        <v>0.0020820613885356772</v>
       </c>
       <c r="D10">
-        <v>-8.152127789576298</v>
+        <v>-8.152127790361705</v>
       </c>
       <c r="E10">
         <v>4.440892098500626e-16</v>
       </c>
       <c r="F10">
-        <v>0.002092672790112544</v>
+        <v>0.002092672790355289</v>
       </c>
       <c r="G10">
-        <v>-8.110790460839</v>
+        <v>-8.110790461340638</v>
       </c>
       <c r="H10">
         <v>4.440892098500626e-16</v>
@@ -765,22 +765,22 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>-0.05840936654059832</v>
+        <v>-0.05840936654836825</v>
       </c>
       <c r="C11">
-        <v>0.002412569464141867</v>
+        <v>0.0024125694644756158</v>
       </c>
       <c r="D11">
-        <v>-24.210439288376758</v>
+        <v>-24.21043928824815</v>
       </c>
       <c r="E11">
         <v>0.0</v>
       </c>
       <c r="F11">
-        <v>0.002432147967665767</v>
+        <v>0.0024321479682888726</v>
       </c>
       <c r="G11">
-        <v>-24.01554811513224</v>
+        <v>-24.01554811217424</v>
       </c>
       <c r="H11">
         <v>0.0</v>
@@ -791,22 +791,22 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>0.02450302355107599</v>
+        <v>0.024503023553541652</v>
       </c>
       <c r="C12">
-        <v>0.0022796709937511297</v>
+        <v>0.0022796709939062365</v>
       </c>
       <c r="D12">
-        <v>10.748491171858534</v>
+        <v>10.748491172208803</v>
       </c>
       <c r="E12">
         <v>0.0</v>
       </c>
       <c r="F12">
-        <v>0.002217588037745688</v>
+        <v>0.0022175880380344393</v>
       </c>
       <c r="G12">
-        <v>11.049402834975963</v>
+        <v>11.049402834649092</v>
       </c>
       <c r="H12">
         <v>0.0</v>
@@ -817,22 +817,22 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.32940733303679803</v>
+        <v>0.32940733301306524</v>
       </c>
       <c r="C13">
-        <v>0.04059328792812295</v>
+        <v>0.04059328793012442</v>
       </c>
       <c r="D13">
-        <v>8.114822667729392</v>
+        <v>8.11482266674464</v>
       </c>
       <c r="E13">
         <v>4.440892098500626e-16</v>
       </c>
       <c r="F13">
-        <v>0.040195959143146935</v>
+        <v>0.04019595914587231</v>
       </c>
       <c r="G13">
-        <v>8.195036020006482</v>
+        <v>8.195036018860414</v>
       </c>
       <c r="H13">
         <v>2.220446049250313e-16</v>
@@ -869,22 +869,22 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>-0.012462263200711435</v>
+        <v>-0.012462263204997246</v>
       </c>
       <c r="C15">
-        <v>0.002028365027907285</v>
+        <v>0.002028365028090708</v>
       </c>
       <c r="D15">
-        <v>-6.143994315248604</v>
+        <v>-6.143994316805948</v>
       </c>
       <c r="E15">
         <v>8.047171817793242e-10</v>
       </c>
       <c r="F15">
-        <v>0.0020942008475180983</v>
+        <v>0.002094200847780944</v>
       </c>
       <c r="G15">
-        <v>-5.950844311557244</v>
+        <v>-5.95084431285686</v>
       </c>
       <c r="H15">
         <v>2.6676274522685617e-9</v>
@@ -895,22 +895,22 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <v>-0.016548005087206805</v>
+        <v>-0.01654800508971817</v>
       </c>
       <c r="C16">
-        <v>0.0012441571772742635</v>
+        <v>0.0012441571773924194</v>
       </c>
       <c r="D16">
-        <v>-13.300574388406991</v>
+        <v>-13.300574389162382</v>
       </c>
       <c r="E16">
         <v>0.0</v>
       </c>
       <c r="F16">
-        <v>0.0012276693379649358</v>
+        <v>0.001227669338140825</v>
       </c>
       <c r="G16">
-        <v>-13.479203703692601</v>
+        <v>-13.47920370380706</v>
       </c>
       <c r="H16">
         <v>0.0</v>
@@ -921,22 +921,22 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>-0.010496172028333117</v>
+        <v>-0.010496172029904414</v>
       </c>
       <c r="C17">
-        <v>0.000727807720747097</v>
+        <v>0.0007278077207773277</v>
       </c>
       <c r="D17">
-        <v>-14.421627758439772</v>
+        <v>-14.421627759999692</v>
       </c>
       <c r="E17">
         <v>0.0</v>
       </c>
       <c r="F17">
-        <v>0.0007428072116790085</v>
+        <v>0.0007428072117377957</v>
       </c>
       <c r="G17">
-        <v>-14.130412122154866</v>
+        <v>-14.130412123151908</v>
       </c>
       <c r="H17">
         <v>0.0</v>
@@ -947,22 +947,22 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>-0.0060759833686522425</v>
+        <v>-0.006075983368030862</v>
       </c>
       <c r="C18">
-        <v>0.0005077889036367481</v>
+        <v>0.0005077889036588179</v>
       </c>
       <c r="D18">
-        <v>-11.965569403223427</v>
+        <v>-11.965569401479675</v>
       </c>
       <c r="E18">
         <v>0.0</v>
       </c>
       <c r="F18">
-        <v>0.0005244251308124446</v>
+        <v>0.0005244251308454061</v>
       </c>
       <c r="G18">
-        <v>-11.585988183364266</v>
+        <v>-11.585988181451176</v>
       </c>
       <c r="H18">
         <v>0.0</v>
@@ -973,25 +973,25 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>-0.005175565601063281</v>
+        <v>-0.0051755656037607645</v>
       </c>
       <c r="C19">
-        <v>0.0013955103691924578</v>
+        <v>0.0013955103692973629</v>
       </c>
       <c r="D19">
-        <v>-3.7087260082905966</v>
+        <v>-3.7087260099447725</v>
       </c>
       <c r="E19">
-        <v>0.00020830468216392894</v>
+        <v>0.0002083046808032396</v>
       </c>
       <c r="F19">
-        <v>0.0013667576453738832</v>
+        <v>0.0013667576455155279</v>
       </c>
       <c r="G19">
-        <v>-3.786747137344514</v>
+        <v>-3.7867471389257097</v>
       </c>
       <c r="H19">
-        <v>0.00015263228312267785</v>
+        <v>0.00015263228215189883</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -999,22 +999,22 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>0.7710501385230064</v>
+        <v>0.771050138576526</v>
       </c>
       <c r="C20">
-        <v>0.04705073977335585</v>
+        <v>0.04705073977644925</v>
       </c>
       <c r="D20">
-        <v>16.38763050777027</v>
+        <v>16.387630507830334</v>
       </c>
       <c r="E20">
         <v>0.0</v>
       </c>
       <c r="F20">
-        <v>0.04684840760994011</v>
+        <v>0.046848407615026344</v>
       </c>
       <c r="G20">
-        <v>16.458406546979585</v>
+        <v>16.458406546335127</v>
       </c>
       <c r="H20">
         <v>0.0</v>
@@ -1025,22 +1025,22 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>0.6324353695978845</v>
+        <v>0.6324353696331491</v>
       </c>
       <c r="C21">
-        <v>0.028521615146793463</v>
+        <v>0.028521615148464945</v>
       </c>
       <c r="D21">
-        <v>22.17389745787191</v>
+        <v>22.173897457808845</v>
       </c>
       <c r="E21">
         <v>0.0</v>
       </c>
       <c r="F21">
-        <v>0.028264481126689854</v>
+        <v>0.028264481130867776</v>
       </c>
       <c r="G21">
-        <v>22.375622844909838</v>
+        <v>22.375622842850046</v>
       </c>
       <c r="H21">
         <v>0.0</v>
@@ -1061,7 +1061,7 @@
         <v>28</v>
       </c>
       <c r="B1">
-        <v>-4774.551387693236</v>
+        <v>-4774.551387693233</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1077,7 +1077,7 @@
         <v>30</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.684807062149048</v>
+        <v>5.967043161392212</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1125,7 +1125,7 @@
         <v>37</v>
       </c>
       <c r="B9">
-        <v>9585.102775386473</v>
+        <v>9585.102775386466</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1133,7 +1133,7 @@
         <v>38</v>
       </c>
       <c r="B10">
-        <v>9708.468753091147</v>
+        <v>9708.46875309114</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1141,7 +1141,7 @@
         <v>39</v>
       </c>
       <c r="B11">
-        <v>0.41745492598445966</v>
+        <v>0.4174549259844601</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/NL_modeChoice_SP.xlsx
+++ b/examples/output/NL_modeChoice_SP.xlsx
@@ -1101,7 +1101,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>5.967043161392212</v>
+        <v>6.024702072143555</v>
       </c>
     </row>
     <row r="7" spans="1:2">
